--- a/Excel/Datas/__tables__.xlsx
+++ b/Excel/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200"/>
+    <workbookView windowWidth="30240" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,24 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>PokemonTable</t>
+  </si>
+  <si>
+    <t>PokemonConfig</t>
+  </si>
+  <si>
+    <t>pokemon_table@pokemon.xlsx</t>
+  </si>
+  <si>
+    <t>ItemTable</t>
+  </si>
+  <si>
+    <t>ItemConfig</t>
+  </si>
+  <si>
+    <t>item_table@item.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1279,16 +1297,33 @@
       </c>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4"/>
-      <c r="E4" s="13"/>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="E5" s="13"/>
+      <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="2:5">
       <c r="B6" s="5"/>
@@ -1314,6 +1349,10 @@
       <c r="C11" s="12"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" display="pokemon_table@pokemon.xlsx" tooltip="mailto:pokemon_table@pokemon.xlsx"/>
+    <hyperlink ref="E5" r:id="rId2" display="item_table@item.xlsx" tooltip="mailto:item_table@item.xlsx"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Excel/Datas/__tables__.xlsx
+++ b/Excel/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,15 @@
   </si>
   <si>
     <t>item_table@item.xlsx</t>
+  </si>
+  <si>
+    <t>BuffTable</t>
+  </si>
+  <si>
+    <t>BuffConfig</t>
+  </si>
+  <si>
+    <t>buff_table@buff.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1326,9 +1335,18 @@
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="E6" s="13"/>
+      <c r="B6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="2:5">
       <c r="B7" s="7"/>
@@ -1352,6 +1370,7 @@
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="pokemon_table@pokemon.xlsx" tooltip="mailto:pokemon_table@pokemon.xlsx"/>
     <hyperlink ref="E5" r:id="rId2" display="item_table@item.xlsx" tooltip="mailto:item_table@item.xlsx"/>
+    <hyperlink ref="E6" r:id="rId3" display="buff_table@buff.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/Datas/__tables__.xlsx
+++ b/Excel/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,51 @@
   </si>
   <si>
     <t>buff_table@buff.xlsx</t>
+  </si>
+  <si>
+    <t>PassiveTable</t>
+  </si>
+  <si>
+    <t>PassiveConfig</t>
+  </si>
+  <si>
+    <t>passive_table@passive.xlsx</t>
+  </si>
+  <si>
+    <t>EnemyPowerTable</t>
+  </si>
+  <si>
+    <t>EnemyPowerConfig</t>
+  </si>
+  <si>
+    <t>enemy_power_table@game.xlsx</t>
+  </si>
+  <si>
+    <t>TerrainCardTable</t>
+  </si>
+  <si>
+    <t>TerrainCardConfig</t>
+  </si>
+  <si>
+    <t>card_terrain_table@card_terrain.xlsx</t>
+  </si>
+  <si>
+    <t>ItemCardTable</t>
+  </si>
+  <si>
+    <t>ItemCardConfig</t>
+  </si>
+  <si>
+    <t>card_item_table@card_item.xlsx</t>
+  </si>
+  <si>
+    <t>BuildingCardTable</t>
+  </si>
+  <si>
+    <t>BuildingCardConfig</t>
+  </si>
+  <si>
+    <t>card_building_table@card_building.xlsx</t>
   </si>
 </sst>
 </file>
@@ -500,7 +545,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -571,17 +616,6 @@
       <bottom style="thin">
         <color theme="2"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="2"/>
-      </left>
-      <right style="thin">
-        <color theme="2"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -717,7 +751,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -729,34 +763,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -841,7 +875,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -872,13 +906,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="22" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
@@ -1203,7 +1231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="27.625" customWidth="1"/>
@@ -1315,7 +1343,7 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="11" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="1"/>
@@ -1330,7 +1358,7 @@
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="11" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1344,33 +1372,138 @@
       <c r="D6" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="7"/>
-      <c r="C7" s="6"/>
-      <c r="E7" s="13"/>
+      <c r="B7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="E8" s="13"/>
+      <c r="B8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="E9" s="13"/>
-    </row>
-    <row r="11" spans="3:3">
-      <c r="C11" s="12"/>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="5:5">
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="5:5">
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="5:5">
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="5:5">
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="5:5">
+      <c r="E16" s="11"/>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" s="11"/>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20" s="11"/>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="5:5">
+      <c r="E22" s="11"/>
+    </row>
+    <row r="23" spans="5:5">
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" spans="5:5">
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25" spans="5:5">
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" spans="5:5">
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" spans="5:5">
+      <c r="E27" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="pokemon_table@pokemon.xlsx" tooltip="mailto:pokemon_table@pokemon.xlsx"/>
     <hyperlink ref="E5" r:id="rId2" display="item_table@item.xlsx" tooltip="mailto:item_table@item.xlsx"/>
     <hyperlink ref="E6" r:id="rId3" display="buff_table@buff.xlsx"/>
+    <hyperlink ref="E7" r:id="rId4" display="passive_table@passive.xlsx"/>
+    <hyperlink ref="E8" r:id="rId5" display="enemy_power_table@game.xlsx"/>
+    <hyperlink ref="E9" r:id="rId6" display="card_terrain_table@card_terrain.xlsx" tooltip="mailto:card_terrain_table@card_terrain.xlsx"/>
+    <hyperlink ref="E10" r:id="rId7" display="card_item_table@card_item.xlsx" tooltip="mailto:card_item_table@card_item.xlsx"/>
+    <hyperlink ref="E11" r:id="rId8" display="card_building_table@card_building.xlsx" tooltip="mailto:card_building_table@card_building.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/Datas/__tables__.xlsx
+++ b/Excel/Datas/__tables__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0328188C-8EFC-4992-9E63-FC42D1574BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -164,15 +168,6 @@
     <t>card_terrain_table@card_terrain.xlsx</t>
   </si>
   <si>
-    <t>ItemCardTable</t>
-  </si>
-  <si>
-    <t>ItemCardConfig</t>
-  </si>
-  <si>
-    <t>card_item_table@card_item.xlsx</t>
-  </si>
-  <si>
     <t>BuildingCardTable</t>
   </si>
   <si>
@@ -180,19 +175,37 @@
   </si>
   <si>
     <t>card_building_table@card_building.xlsx</t>
+  </si>
+  <si>
+    <t>card_index_table@index.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardIndex</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardIndexTable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectCardTable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectCardConfig</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>card_effect_table@card_effect.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,136 +229,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,188 +262,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -627,347 +345,72 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="22" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="22" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="22" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="22" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="22" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="好" xfId="2" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1225,14 +668,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.625" customWidth="1"/>
     <col min="3" max="3" width="22.625" customWidth="1"/>
@@ -1242,7 +685,7 @@
     <col min="7" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1277,7 +720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1309,7 +752,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    <row r="3" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1333,7 +776,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1348,7 +791,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="3" t="s">
         <v>30</v>
       </c>
@@ -1362,7 +805,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
         <v>33</v>
       </c>
@@ -1376,7 +819,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7" s="7" t="s">
         <v>36</v>
       </c>
@@ -1390,7 +833,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8" s="8" t="s">
         <v>39</v>
       </c>
@@ -1404,7 +847,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>42</v>
       </c>
@@ -1418,95 +861,107 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B10" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B12" s="12" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="5:5">
-      <c r="E12" s="11"/>
-    </row>
-    <row r="13" spans="5:5">
+      <c r="C12" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E13" s="11"/>
     </row>
-    <row r="14" spans="5:5">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E14" s="11"/>
     </row>
-    <row r="15" spans="5:5">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="5:5">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E16" s="11"/>
     </row>
-    <row r="17" spans="5:5">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E17" s="11"/>
     </row>
-    <row r="18" spans="5:5">
+    <row r="18" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E18" s="11"/>
     </row>
-    <row r="19" spans="5:5">
+    <row r="19" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E19" s="11"/>
     </row>
-    <row r="20" spans="5:5">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E20" s="11"/>
     </row>
-    <row r="21" spans="5:5">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E21" s="11"/>
     </row>
-    <row r="22" spans="5:5">
+    <row r="22" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E22" s="11"/>
     </row>
-    <row r="23" spans="5:5">
+    <row r="23" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E23" s="11"/>
     </row>
-    <row r="24" spans="5:5">
+    <row r="24" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E24" s="11"/>
     </row>
-    <row r="25" spans="5:5">
+    <row r="25" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E25" s="11"/>
     </row>
-    <row r="26" spans="5:5">
+    <row r="26" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E26" s="11"/>
     </row>
-    <row r="27" spans="5:5">
+    <row r="27" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E27" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" display="pokemon_table@pokemon.xlsx" tooltip="mailto:pokemon_table@pokemon.xlsx"/>
-    <hyperlink ref="E5" r:id="rId2" display="item_table@item.xlsx" tooltip="mailto:item_table@item.xlsx"/>
-    <hyperlink ref="E6" r:id="rId3" display="buff_table@buff.xlsx"/>
-    <hyperlink ref="E7" r:id="rId4" display="passive_table@passive.xlsx"/>
-    <hyperlink ref="E8" r:id="rId5" display="enemy_power_table@game.xlsx"/>
-    <hyperlink ref="E9" r:id="rId6" display="card_terrain_table@card_terrain.xlsx" tooltip="mailto:card_terrain_table@card_terrain.xlsx"/>
-    <hyperlink ref="E10" r:id="rId7" display="card_item_table@card_item.xlsx" tooltip="mailto:card_item_table@card_item.xlsx"/>
-    <hyperlink ref="E11" r:id="rId8" display="card_building_table@card_building.xlsx" tooltip="mailto:card_building_table@card_building.xlsx"/>
+    <hyperlink ref="E4" r:id="rId1" tooltip="mailto:pokemon_table@pokemon.xlsx" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId2" tooltip="mailto:item_table@item.xlsx" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="E8" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="E9" r:id="rId6" tooltip="mailto:card_terrain_table@card_terrain.xlsx" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="E10" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="E11" r:id="rId8" tooltip="mailto:card_building_table@card_building.xlsx" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="E12" r:id="rId9" xr:uid="{E65F4382-6DCB-4339-8B70-C23D4E153D3A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>